--- a/src/main/resources/cardData.xlsx
+++ b/src/main/resources/cardData.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashto\Documents\CS491\uno3\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE045E70-9987-4244-93A8-6F088C48BFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DBE80F-056E-4E7C-BACB-99FE8409AB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{643BDA9D-5BC1-44C5-834C-2E1825C2823B}"/>
   </bookViews>
   <sheets>
     <sheet name="cardData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="62">
   <si>
     <t>name</t>
   </si>
@@ -190,7 +203,22 @@
     <t>imagePath</t>
   </si>
   <si>
-    <t>horse.png</t>
+    <t>JackHearts.png</t>
+  </si>
+  <si>
+    <t>JackClubs.png</t>
+  </si>
+  <si>
+    <t>JackSpades.png</t>
+  </si>
+  <si>
+    <t>JackDiamonds.png</t>
+  </si>
+  <si>
+    <t>b1fv.png</t>
+  </si>
+  <si>
+    <t>b2fv.png</t>
   </si>
 </sst>
 </file>
@@ -1172,8 +1200,9 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
-        <v>56</v>
+      <c r="F2" t="str">
+        <f>CHOOSE(C2,"Ace","2","3","4","5","6","7","8","9","10","Jack","Queen","King")&amp;CHOOSE(D2,"Hearts","Spades","Clubs","Diamonds")&amp;".png"</f>
+        <v>AceHearts.png</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1192,8 +1221,9 @@
       <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>56</v>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F55" si="0">CHOOSE(C3,"Ace","2","3","4","5","6","7","8","9","10","Jack","Queen","King")&amp;CHOOSE(D3,"Hearts","Spades","Clubs","Diamonds")&amp;".png"</f>
+        <v>2Hearts.png</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1212,8 +1242,9 @@
       <c r="E4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
-        <v>56</v>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>3Hearts.png</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1232,8 +1263,9 @@
       <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" t="s">
-        <v>56</v>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>4Hearts.png</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1252,8 +1284,9 @@
       <c r="E6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" t="s">
-        <v>56</v>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>5Hearts.png</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1272,8 +1305,9 @@
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" t="s">
-        <v>56</v>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>6Hearts.png</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1292,8 +1326,9 @@
       <c r="E8" t="s">
         <v>11</v>
       </c>
-      <c r="F8" t="s">
-        <v>56</v>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>7Hearts.png</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1312,8 +1347,9 @@
       <c r="E9" t="s">
         <v>12</v>
       </c>
-      <c r="F9" t="s">
-        <v>56</v>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>8Hearts.png</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1332,8 +1368,9 @@
       <c r="E10" t="s">
         <v>13</v>
       </c>
-      <c r="F10" t="s">
-        <v>56</v>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>9Hearts.png</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1352,8 +1389,9 @@
       <c r="E11" t="s">
         <v>41</v>
       </c>
-      <c r="F11" t="s">
-        <v>56</v>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>10Hearts.png</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1372,8 +1410,9 @@
       <c r="E12" t="s">
         <v>49</v>
       </c>
-      <c r="F12" t="s">
-        <v>56</v>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>QueenHearts.png</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1392,8 +1431,9 @@
       <c r="E13" t="s">
         <v>45</v>
       </c>
-      <c r="F13" t="s">
-        <v>56</v>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>KingHearts.png</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1412,8 +1452,9 @@
       <c r="E14" t="s">
         <v>14</v>
       </c>
-      <c r="F14" t="s">
-        <v>56</v>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>AceSpades.png</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1432,8 +1473,9 @@
       <c r="E15" t="s">
         <v>15</v>
       </c>
-      <c r="F15" t="s">
-        <v>56</v>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>2Spades.png</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1452,8 +1494,9 @@
       <c r="E16" t="s">
         <v>16</v>
       </c>
-      <c r="F16" t="s">
-        <v>56</v>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>3Spades.png</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -1472,8 +1515,9 @@
       <c r="E17" t="s">
         <v>17</v>
       </c>
-      <c r="F17" t="s">
-        <v>56</v>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>4Spades.png</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1492,8 +1536,9 @@
       <c r="E18" t="s">
         <v>18</v>
       </c>
-      <c r="F18" t="s">
-        <v>56</v>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v>5Spades.png</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1512,8 +1557,9 @@
       <c r="E19" t="s">
         <v>19</v>
       </c>
-      <c r="F19" t="s">
-        <v>56</v>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v>6Spades.png</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1532,8 +1578,9 @@
       <c r="E20" t="s">
         <v>20</v>
       </c>
-      <c r="F20" t="s">
-        <v>56</v>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v>7Spades.png</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1552,8 +1599,9 @@
       <c r="E21" t="s">
         <v>21</v>
       </c>
-      <c r="F21" t="s">
-        <v>56</v>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v>8Spades.png</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1572,8 +1620,9 @@
       <c r="E22" t="s">
         <v>22</v>
       </c>
-      <c r="F22" t="s">
-        <v>56</v>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v>9Spades.png</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1592,8 +1641,9 @@
       <c r="E23" t="s">
         <v>42</v>
       </c>
-      <c r="F23" t="s">
-        <v>56</v>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v>10Spades.png</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1612,8 +1662,9 @@
       <c r="E24" t="s">
         <v>50</v>
       </c>
-      <c r="F24" t="s">
-        <v>56</v>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v>QueenSpades.png</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -1632,8 +1683,9 @@
       <c r="E25" t="s">
         <v>46</v>
       </c>
-      <c r="F25" t="s">
-        <v>56</v>
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v>KingSpades.png</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -1652,8 +1704,9 @@
       <c r="E26" t="s">
         <v>23</v>
       </c>
-      <c r="F26" t="s">
-        <v>56</v>
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v>AceClubs.png</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -1672,8 +1725,9 @@
       <c r="E27" t="s">
         <v>24</v>
       </c>
-      <c r="F27" t="s">
-        <v>56</v>
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v>2Clubs.png</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -1692,8 +1746,9 @@
       <c r="E28" t="s">
         <v>25</v>
       </c>
-      <c r="F28" t="s">
-        <v>56</v>
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v>3Clubs.png</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -1712,8 +1767,9 @@
       <c r="E29" t="s">
         <v>26</v>
       </c>
-      <c r="F29" t="s">
-        <v>56</v>
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v>4Clubs.png</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1732,8 +1788,9 @@
       <c r="E30" t="s">
         <v>27</v>
       </c>
-      <c r="F30" t="s">
-        <v>56</v>
+      <c r="F30" t="str">
+        <f t="shared" si="0"/>
+        <v>5Clubs.png</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1752,8 +1809,9 @@
       <c r="E31" t="s">
         <v>28</v>
       </c>
-      <c r="F31" t="s">
-        <v>56</v>
+      <c r="F31" t="str">
+        <f t="shared" si="0"/>
+        <v>6Clubs.png</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -1772,8 +1830,9 @@
       <c r="E32" t="s">
         <v>29</v>
       </c>
-      <c r="F32" t="s">
-        <v>56</v>
+      <c r="F32" t="str">
+        <f t="shared" si="0"/>
+        <v>7Clubs.png</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1792,8 +1851,9 @@
       <c r="E33" t="s">
         <v>30</v>
       </c>
-      <c r="F33" t="s">
-        <v>56</v>
+      <c r="F33" t="str">
+        <f t="shared" si="0"/>
+        <v>8Clubs.png</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1812,8 +1872,9 @@
       <c r="E34" t="s">
         <v>31</v>
       </c>
-      <c r="F34" t="s">
-        <v>56</v>
+      <c r="F34" t="str">
+        <f t="shared" si="0"/>
+        <v>9Clubs.png</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1832,8 +1893,9 @@
       <c r="E35" t="s">
         <v>43</v>
       </c>
-      <c r="F35" t="s">
-        <v>56</v>
+      <c r="F35" t="str">
+        <f t="shared" si="0"/>
+        <v>10Clubs.png</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1852,8 +1914,9 @@
       <c r="E36" t="s">
         <v>51</v>
       </c>
-      <c r="F36" t="s">
-        <v>56</v>
+      <c r="F36" t="str">
+        <f t="shared" si="0"/>
+        <v>QueenClubs.png</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -1872,8 +1935,9 @@
       <c r="E37" t="s">
         <v>47</v>
       </c>
-      <c r="F37" t="s">
-        <v>56</v>
+      <c r="F37" t="str">
+        <f t="shared" si="0"/>
+        <v>KingClubs.png</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1892,8 +1956,9 @@
       <c r="E38" t="s">
         <v>32</v>
       </c>
-      <c r="F38" t="s">
-        <v>56</v>
+      <c r="F38" t="str">
+        <f t="shared" si="0"/>
+        <v>AceDiamonds.png</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -1912,8 +1977,9 @@
       <c r="E39" t="s">
         <v>33</v>
       </c>
-      <c r="F39" t="s">
-        <v>56</v>
+      <c r="F39" t="str">
+        <f t="shared" si="0"/>
+        <v>2Diamonds.png</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -1932,8 +1998,9 @@
       <c r="E40" t="s">
         <v>34</v>
       </c>
-      <c r="F40" t="s">
-        <v>56</v>
+      <c r="F40" t="str">
+        <f t="shared" si="0"/>
+        <v>3Diamonds.png</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1952,8 +2019,9 @@
       <c r="E41" t="s">
         <v>35</v>
       </c>
-      <c r="F41" t="s">
-        <v>56</v>
+      <c r="F41" t="str">
+        <f t="shared" si="0"/>
+        <v>4Diamonds.png</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -1972,8 +2040,9 @@
       <c r="E42" t="s">
         <v>36</v>
       </c>
-      <c r="F42" t="s">
-        <v>56</v>
+      <c r="F42" t="str">
+        <f t="shared" si="0"/>
+        <v>5Diamonds.png</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1992,8 +2061,9 @@
       <c r="E43" t="s">
         <v>37</v>
       </c>
-      <c r="F43" t="s">
-        <v>56</v>
+      <c r="F43" t="str">
+        <f t="shared" si="0"/>
+        <v>6Diamonds.png</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2012,8 +2082,9 @@
       <c r="E44" t="s">
         <v>38</v>
       </c>
-      <c r="F44" t="s">
-        <v>56</v>
+      <c r="F44" t="str">
+        <f t="shared" si="0"/>
+        <v>7Diamonds.png</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2032,8 +2103,9 @@
       <c r="E45" t="s">
         <v>39</v>
       </c>
-      <c r="F45" t="s">
-        <v>56</v>
+      <c r="F45" t="str">
+        <f t="shared" si="0"/>
+        <v>8Diamonds.png</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2052,8 +2124,9 @@
       <c r="E46" t="s">
         <v>40</v>
       </c>
-      <c r="F46" t="s">
-        <v>56</v>
+      <c r="F46" t="str">
+        <f t="shared" si="0"/>
+        <v>9Diamonds.png</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2072,8 +2145,9 @@
       <c r="E47" t="s">
         <v>44</v>
       </c>
-      <c r="F47" t="s">
-        <v>56</v>
+      <c r="F47" t="str">
+        <f t="shared" si="0"/>
+        <v>10Diamonds.png</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2092,8 +2166,9 @@
       <c r="E48" t="s">
         <v>52</v>
       </c>
-      <c r="F48" t="s">
-        <v>56</v>
+      <c r="F48" t="str">
+        <f t="shared" si="0"/>
+        <v>QueenDiamonds.png</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2112,8 +2187,9 @@
       <c r="E49" t="s">
         <v>48</v>
       </c>
-      <c r="F49" t="s">
-        <v>56</v>
+      <c r="F49" t="str">
+        <f t="shared" si="0"/>
+        <v>KingDiamonds.png</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2153,7 +2229,7 @@
         <v>53</v>
       </c>
       <c r="F51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2173,7 +2249,7 @@
         <v>53</v>
       </c>
       <c r="F52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2193,7 +2269,7 @@
         <v>53</v>
       </c>
       <c r="F53" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2213,7 +2289,7 @@
         <v>54</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2233,7 +2309,7 @@
         <v>54</v>
       </c>
       <c r="F55" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
